--- a/inst/extdata/national_mortality.xlsx
+++ b/inst/extdata/national_mortality.xlsx
@@ -121,7 +121,7 @@
     <t>dm2</t>
   </si>
   <si>
-    <t>cause</t>
+    <t>allcause</t>
   </si>
 </sst>
 </file>
